--- a/docs/public/template/kas-masuk-keluar.xlsx
+++ b/docs/public/template/kas-masuk-keluar.xlsx
@@ -398,16 +398,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:H17"/>
   <cols>
     <col min="1" max="1" width="5.83203125" customWidth="1"/>
     <col min="2" max="2" width="12.83203125" customWidth="1"/>
     <col min="3" max="3" width="12.83203125" customWidth="1"/>
-    <col min="4" max="4" width="30.83203125" customWidth="1"/>
+    <col min="4" max="4" width="35.83203125" customWidth="1"/>
     <col min="5" max="5" width="15.83203125" customWidth="1"/>
     <col min="6" max="6" width="15.83203125" customWidth="1"/>
     <col min="7" max="7" width="30.83203125" customWidth="1"/>
-    <col min="8" max="8" width="20.83203125" customWidth="1"/>
+    <col min="8" max="8" width="15.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -421,13 +421,13 @@
         <v>Jenis</v>
       </c>
       <c r="D1" t="str">
-        <v>Sumber/Tujuan</v>
+        <v>Sumber / Tujuan</v>
       </c>
       <c r="E1" t="str">
-        <v>Jumlah</v>
+        <v>Jumlah (Rp)</v>
       </c>
       <c r="F1" t="str">
-        <v>Saldo</v>
+        <v>Saldo (Rp)</v>
       </c>
       <c r="G1" t="str">
         <v>Keterangan</v>
@@ -438,22 +438,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v/>
+        <v>1</v>
       </c>
       <c r="B2" t="str">
-        <v/>
+        <v>01/06/2025</v>
       </c>
       <c r="C2" t="str">
-        <v/>
+        <v>Pemasukan</v>
       </c>
       <c r="D2" t="str">
-        <v/>
+        <v>Infak Kotak Harian (Senin-Jumat)</v>
       </c>
       <c r="E2" t="str">
-        <v/>
+        <v>150.000</v>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>450.000</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -464,48 +464,48 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v/>
+        <v>2</v>
       </c>
       <c r="B3" t="str">
-        <v/>
+        <v>03/06/2025</v>
       </c>
       <c r="C3" t="str">
-        <v/>
+        <v>Pengeluaran</v>
       </c>
       <c r="D3" t="str">
-        <v/>
+        <v>Beli Sabun Cuci Tangan (3 botol)</v>
       </c>
       <c r="E3" t="str">
-        <v/>
+        <v>45.000</v>
       </c>
       <c r="F3" t="str">
-        <v/>
+        <v>405.000</v>
       </c>
       <c r="G3" t="str">
-        <v/>
+        <v>Toko Berkah</v>
       </c>
       <c r="H3" t="str">
-        <v/>
+        <v>Ada nota</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v/>
+        <v>3</v>
       </c>
       <c r="B4" t="str">
-        <v/>
+        <v>06/06/2025</v>
       </c>
       <c r="C4" t="str">
-        <v/>
+        <v>Pemasukan</v>
       </c>
       <c r="D4" t="str">
-        <v/>
+        <v>Infak Jumat</v>
       </c>
       <c r="E4" t="str">
-        <v/>
+        <v>350.000</v>
       </c>
       <c r="F4" t="str">
-        <v/>
+        <v>755.000</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -516,80 +516,80 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v/>
+        <v>4</v>
       </c>
       <c r="B5" t="str">
-        <v/>
+        <v>06/06/2025</v>
       </c>
       <c r="C5" t="str">
-        <v/>
+        <v>Pengeluaran</v>
       </c>
       <c r="D5" t="str">
-        <v/>
+        <v>Bayar Listrik Bulan Juni</v>
       </c>
       <c r="E5" t="str">
-        <v/>
+        <v>200.000</v>
       </c>
       <c r="F5" t="str">
-        <v/>
+        <v>555.000</v>
       </c>
       <c r="G5" t="str">
-        <v/>
+        <v>Token 200rb</v>
       </c>
       <c r="H5" t="str">
-        <v/>
+        <v>Struk</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v/>
+        <v>5</v>
       </c>
       <c r="B6" t="str">
-        <v/>
+        <v>15/06/2025</v>
       </c>
       <c r="C6" t="str">
-        <v/>
+        <v>Pemasukan</v>
       </c>
       <c r="D6" t="str">
-        <v/>
+        <v>Donasi Bpk. Surya (transfer bank)</v>
       </c>
       <c r="E6" t="str">
-        <v/>
+        <v>500.000</v>
       </c>
       <c r="F6" t="str">
-        <v/>
+        <v>1.055.000</v>
       </c>
       <c r="G6" t="str">
-        <v/>
+        <v>Untuk perbaikan karpet</v>
       </c>
       <c r="H6" t="str">
-        <v/>
+        <v>Foto transfer</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v/>
+        <v>6</v>
       </c>
       <c r="B7" t="str">
-        <v/>
+        <v>20/06/2025</v>
       </c>
       <c r="C7" t="str">
-        <v/>
+        <v>Pengeluaran</v>
       </c>
       <c r="D7" t="str">
-        <v/>
+        <v>Beli Karpet Baru (4 lembar)</v>
       </c>
       <c r="E7" t="str">
-        <v/>
+        <v>800.000</v>
       </c>
       <c r="F7" t="str">
-        <v/>
+        <v>255.000</v>
       </c>
       <c r="G7" t="str">
-        <v/>
+        <v>Toko Karpet Indah</v>
       </c>
       <c r="H7" t="str">
-        <v/>
+        <v>Kwitansi</v>
       </c>
     </row>
     <row r="8">
@@ -852,127 +852,23 @@
         <v/>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v/>
-      </c>
-      <c r="B18" t="str">
-        <v/>
-      </c>
-      <c r="C18" t="str">
-        <v/>
-      </c>
-      <c r="D18" t="str">
-        <v/>
-      </c>
-      <c r="E18" t="str">
-        <v/>
-      </c>
-      <c r="F18" t="str">
-        <v/>
-      </c>
-      <c r="G18" t="str">
-        <v/>
-      </c>
-      <c r="H18" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v/>
-      </c>
-      <c r="B19" t="str">
-        <v/>
-      </c>
-      <c r="C19" t="str">
-        <v/>
-      </c>
-      <c r="D19" t="str">
-        <v/>
-      </c>
-      <c r="E19" t="str">
-        <v/>
-      </c>
-      <c r="F19" t="str">
-        <v/>
-      </c>
-      <c r="G19" t="str">
-        <v/>
-      </c>
-      <c r="H19" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="str">
-        <v/>
-      </c>
-      <c r="B20" t="str">
-        <v/>
-      </c>
-      <c r="C20" t="str">
-        <v/>
-      </c>
-      <c r="D20" t="str">
-        <v/>
-      </c>
-      <c r="E20" t="str">
-        <v/>
-      </c>
-      <c r="F20" t="str">
-        <v/>
-      </c>
-      <c r="G20" t="str">
-        <v/>
-      </c>
-      <c r="H20" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="str">
-        <v/>
-      </c>
-      <c r="B21" t="str">
-        <v/>
-      </c>
-      <c r="C21" t="str">
-        <v/>
-      </c>
-      <c r="D21" t="str">
-        <v/>
-      </c>
-      <c r="E21" t="str">
-        <v/>
-      </c>
-      <c r="F21" t="str">
-        <v/>
-      </c>
-      <c r="G21" t="str">
-        <v/>
-      </c>
-      <c r="H21" t="str">
-        <v/>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H21"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H17"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F12"/>
   <cols>
     <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="18.83203125" customWidth="1"/>
     <col min="3" max="3" width="18.83203125" customWidth="1"/>
     <col min="4" max="4" width="15.83203125" customWidth="1"/>
     <col min="5" max="5" width="15.83203125" customWidth="1"/>
-    <col min="6" max="6" width="30.83203125" customWidth="1"/>
+    <col min="6" max="6" width="35.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -992,27 +888,27 @@
         <v>Saldo Akhir</v>
       </c>
       <c r="F1" t="str">
-        <v>Catatan Bulanan</v>
+        <v>Catatan</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v/>
+        <v>Juni 2025</v>
       </c>
       <c r="B2" t="str">
-        <v/>
+        <v>Rp 1.000.000</v>
       </c>
       <c r="C2" t="str">
-        <v/>
+        <v>Rp 1.045.000</v>
       </c>
       <c r="D2" t="str">
-        <v/>
+        <v>Rp 300.000</v>
       </c>
       <c r="E2" t="str">
-        <v/>
+        <v>Rp 255.000</v>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>Beli karpet baru (pengeluaran besar). Defisit wajar.</v>
       </c>
     </row>
     <row r="3">
@@ -1215,189 +1111,9 @@
         <v/>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v/>
-      </c>
-      <c r="B13" t="str">
-        <v/>
-      </c>
-      <c r="C13" t="str">
-        <v/>
-      </c>
-      <c r="D13" t="str">
-        <v/>
-      </c>
-      <c r="E13" t="str">
-        <v/>
-      </c>
-      <c r="F13" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v/>
-      </c>
-      <c r="B14" t="str">
-        <v/>
-      </c>
-      <c r="C14" t="str">
-        <v/>
-      </c>
-      <c r="D14" t="str">
-        <v/>
-      </c>
-      <c r="E14" t="str">
-        <v/>
-      </c>
-      <c r="F14" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v/>
-      </c>
-      <c r="B15" t="str">
-        <v/>
-      </c>
-      <c r="C15" t="str">
-        <v/>
-      </c>
-      <c r="D15" t="str">
-        <v/>
-      </c>
-      <c r="E15" t="str">
-        <v/>
-      </c>
-      <c r="F15" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v/>
-      </c>
-      <c r="B16" t="str">
-        <v/>
-      </c>
-      <c r="C16" t="str">
-        <v/>
-      </c>
-      <c r="D16" t="str">
-        <v/>
-      </c>
-      <c r="E16" t="str">
-        <v/>
-      </c>
-      <c r="F16" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v/>
-      </c>
-      <c r="B17" t="str">
-        <v/>
-      </c>
-      <c r="C17" t="str">
-        <v/>
-      </c>
-      <c r="D17" t="str">
-        <v/>
-      </c>
-      <c r="E17" t="str">
-        <v/>
-      </c>
-      <c r="F17" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v/>
-      </c>
-      <c r="B18" t="str">
-        <v/>
-      </c>
-      <c r="C18" t="str">
-        <v/>
-      </c>
-      <c r="D18" t="str">
-        <v/>
-      </c>
-      <c r="E18" t="str">
-        <v/>
-      </c>
-      <c r="F18" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v/>
-      </c>
-      <c r="B19" t="str">
-        <v/>
-      </c>
-      <c r="C19" t="str">
-        <v/>
-      </c>
-      <c r="D19" t="str">
-        <v/>
-      </c>
-      <c r="E19" t="str">
-        <v/>
-      </c>
-      <c r="F19" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="str">
-        <v/>
-      </c>
-      <c r="B20" t="str">
-        <v/>
-      </c>
-      <c r="C20" t="str">
-        <v/>
-      </c>
-      <c r="D20" t="str">
-        <v/>
-      </c>
-      <c r="E20" t="str">
-        <v/>
-      </c>
-      <c r="F20" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="str">
-        <v/>
-      </c>
-      <c r="B21" t="str">
-        <v/>
-      </c>
-      <c r="C21" t="str">
-        <v/>
-      </c>
-      <c r="D21" t="str">
-        <v/>
-      </c>
-      <c r="E21" t="str">
-        <v/>
-      </c>
-      <c r="F21" t="str">
-        <v/>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F21"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F12"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/docs/public/template/kas-masuk-keluar.xlsx
+++ b/docs/public/template/kas-masuk-keluar.xlsx
@@ -403,11 +403,11 @@
     <col min="1" max="1" width="5.83203125" customWidth="1"/>
     <col min="2" max="2" width="12.83203125" customWidth="1"/>
     <col min="3" max="3" width="12.83203125" customWidth="1"/>
-    <col min="4" max="4" width="35.83203125" customWidth="1"/>
-    <col min="5" max="5" width="15.83203125" customWidth="1"/>
-    <col min="6" max="6" width="15.83203125" customWidth="1"/>
+    <col min="4" max="4" width="38.83203125" customWidth="1"/>
+    <col min="5" max="5" width="16.83203125" customWidth="1"/>
+    <col min="6" max="6" width="16.83203125" customWidth="1"/>
     <col min="7" max="7" width="30.83203125" customWidth="1"/>
-    <col min="8" max="8" width="15.83203125" customWidth="1"/>
+    <col min="8" max="8" width="14.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -437,7 +437,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="str">
+      <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="str">
@@ -447,13 +447,13 @@
         <v>Pemasukan</v>
       </c>
       <c r="D2" t="str">
-        <v>Infak Kotak Harian (Senin-Jumat)</v>
-      </c>
-      <c r="E2" t="str">
-        <v>150.000</v>
-      </c>
-      <c r="F2" t="str">
-        <v>450.000</v>
+        <v>Infak Kotak Harian (5 hari)</v>
+      </c>
+      <c r="E2">
+        <v>150000</v>
+      </c>
+      <c r="F2">
+        <v>300000</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -463,7 +463,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="str">
+      <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="str">
@@ -475,21 +475,21 @@
       <c r="D3" t="str">
         <v>Beli Sabun Cuci Tangan (3 botol)</v>
       </c>
-      <c r="E3" t="str">
-        <v>45.000</v>
-      </c>
-      <c r="F3" t="str">
-        <v>405.000</v>
+      <c r="E3">
+        <v>45000</v>
+      </c>
+      <c r="F3">
+        <f>IF(E3="","",FF2+IF(C3="Pemasukan",E3,-E3))</f>
       </c>
       <c r="G3" t="str">
         <v>Toko Berkah</v>
       </c>
       <c r="H3" t="str">
-        <v>Ada nota</v>
+        <v>Nota ada</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="str">
+      <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="str">
@@ -501,11 +501,11 @@
       <c r="D4" t="str">
         <v>Infak Jumat</v>
       </c>
-      <c r="E4" t="str">
-        <v>350.000</v>
-      </c>
-      <c r="F4" t="str">
-        <v>755.000</v>
+      <c r="E4">
+        <v>350000</v>
+      </c>
+      <c r="F4">
+        <f>IF(E4="","",FF3+IF(C4="Pemasukan",E4,-E4))</f>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -515,7 +515,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="str">
+      <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="str">
@@ -525,13 +525,13 @@
         <v>Pengeluaran</v>
       </c>
       <c r="D5" t="str">
-        <v>Bayar Listrik Bulan Juni</v>
-      </c>
-      <c r="E5" t="str">
-        <v>200.000</v>
-      </c>
-      <c r="F5" t="str">
-        <v>555.000</v>
+        <v>Bayar Listrik Juni</v>
+      </c>
+      <c r="E5">
+        <v>200000</v>
+      </c>
+      <c r="F5">
+        <f>IF(E5="","",FF4+IF(C5="Pemasukan",E5,-E5))</f>
       </c>
       <c r="G5" t="str">
         <v>Token 200rb</v>
@@ -541,7 +541,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="str">
+      <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="str">
@@ -551,23 +551,23 @@
         <v>Pemasukan</v>
       </c>
       <c r="D6" t="str">
-        <v>Donasi Bpk. Surya (transfer bank)</v>
-      </c>
-      <c r="E6" t="str">
-        <v>500.000</v>
-      </c>
-      <c r="F6" t="str">
-        <v>1.055.000</v>
+        <v>Donasi Bpk. Surya (transfer)</v>
+      </c>
+      <c r="E6">
+        <v>500000</v>
+      </c>
+      <c r="F6">
+        <f>IF(E6="","",FF5+IF(C6="Pemasukan",E6,-E6))</f>
       </c>
       <c r="G6" t="str">
-        <v>Untuk perbaikan karpet</v>
+        <v>Perbaikan karpet</v>
       </c>
       <c r="H6" t="str">
-        <v>Foto transfer</v>
+        <v>Foto</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="str">
+      <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="str">
@@ -579,11 +579,11 @@
       <c r="D7" t="str">
         <v>Beli Karpet Baru (4 lembar)</v>
       </c>
-      <c r="E7" t="str">
-        <v>800.000</v>
-      </c>
-      <c r="F7" t="str">
-        <v>255.000</v>
+      <c r="E7">
+        <v>800000</v>
+      </c>
+      <c r="F7">
+        <f>IF(E7="","",FF6+IF(C7="Pemasukan",E7,-E7))</f>
       </c>
       <c r="G7" t="str">
         <v>Toko Karpet Indah</v>
@@ -593,263 +593,53 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="str">
-        <v/>
-      </c>
-      <c r="B8" t="str">
-        <v/>
-      </c>
-      <c r="C8" t="str">
-        <v/>
-      </c>
-      <c r="D8" t="str">
-        <v/>
-      </c>
-      <c r="E8" t="str">
-        <v/>
-      </c>
-      <c r="F8" t="str">
-        <v/>
-      </c>
-      <c r="G8" t="str">
-        <v/>
-      </c>
-      <c r="H8" t="str">
-        <v/>
+      <c r="F8">
+        <f>IF(E8="","",FF7+IF(C8="Pemasukan",E8,-E8))</f>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="str">
-        <v/>
-      </c>
-      <c r="B9" t="str">
-        <v/>
-      </c>
-      <c r="C9" t="str">
-        <v/>
-      </c>
-      <c r="D9" t="str">
-        <v/>
-      </c>
-      <c r="E9" t="str">
-        <v/>
-      </c>
-      <c r="F9" t="str">
-        <v/>
-      </c>
-      <c r="G9" t="str">
-        <v/>
-      </c>
-      <c r="H9" t="str">
-        <v/>
+      <c r="F9">
+        <f>IF(E9="","",FF8+IF(C9="Pemasukan",E9,-E9))</f>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="str">
-        <v/>
-      </c>
-      <c r="B10" t="str">
-        <v/>
-      </c>
-      <c r="C10" t="str">
-        <v/>
-      </c>
-      <c r="D10" t="str">
-        <v/>
-      </c>
-      <c r="E10" t="str">
-        <v/>
-      </c>
-      <c r="F10" t="str">
-        <v/>
-      </c>
-      <c r="G10" t="str">
-        <v/>
-      </c>
-      <c r="H10" t="str">
-        <v/>
+      <c r="F10">
+        <f>IF(E10="","",FF9+IF(C10="Pemasukan",E10,-E10))</f>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="str">
-        <v/>
-      </c>
-      <c r="B11" t="str">
-        <v/>
-      </c>
-      <c r="C11" t="str">
-        <v/>
-      </c>
-      <c r="D11" t="str">
-        <v/>
-      </c>
-      <c r="E11" t="str">
-        <v/>
-      </c>
-      <c r="F11" t="str">
-        <v/>
-      </c>
-      <c r="G11" t="str">
-        <v/>
-      </c>
-      <c r="H11" t="str">
-        <v/>
+      <c r="F11">
+        <f>IF(E11="","",FF10+IF(C11="Pemasukan",E11,-E11))</f>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="str">
-        <v/>
-      </c>
-      <c r="B12" t="str">
-        <v/>
-      </c>
-      <c r="C12" t="str">
-        <v/>
-      </c>
-      <c r="D12" t="str">
-        <v/>
-      </c>
-      <c r="E12" t="str">
-        <v/>
-      </c>
-      <c r="F12" t="str">
-        <v/>
-      </c>
-      <c r="G12" t="str">
-        <v/>
-      </c>
-      <c r="H12" t="str">
-        <v/>
+      <c r="F12">
+        <f>IF(E12="","",FF11+IF(C12="Pemasukan",E12,-E12))</f>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="str">
-        <v/>
-      </c>
-      <c r="B13" t="str">
-        <v/>
-      </c>
-      <c r="C13" t="str">
-        <v/>
-      </c>
-      <c r="D13" t="str">
-        <v/>
-      </c>
-      <c r="E13" t="str">
-        <v/>
-      </c>
-      <c r="F13" t="str">
-        <v/>
-      </c>
-      <c r="G13" t="str">
-        <v/>
-      </c>
-      <c r="H13" t="str">
-        <v/>
+      <c r="F13">
+        <f>IF(E13="","",FF12+IF(C13="Pemasukan",E13,-E13))</f>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="str">
-        <v/>
-      </c>
-      <c r="B14" t="str">
-        <v/>
-      </c>
-      <c r="C14" t="str">
-        <v/>
-      </c>
-      <c r="D14" t="str">
-        <v/>
-      </c>
-      <c r="E14" t="str">
-        <v/>
-      </c>
-      <c r="F14" t="str">
-        <v/>
-      </c>
-      <c r="G14" t="str">
-        <v/>
-      </c>
-      <c r="H14" t="str">
-        <v/>
+      <c r="F14">
+        <f>IF(E14="","",FF13+IF(C14="Pemasukan",E14,-E14))</f>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="str">
-        <v/>
-      </c>
-      <c r="B15" t="str">
-        <v/>
-      </c>
-      <c r="C15" t="str">
-        <v/>
-      </c>
-      <c r="D15" t="str">
-        <v/>
-      </c>
-      <c r="E15" t="str">
-        <v/>
-      </c>
-      <c r="F15" t="str">
-        <v/>
-      </c>
-      <c r="G15" t="str">
-        <v/>
-      </c>
-      <c r="H15" t="str">
-        <v/>
+      <c r="F15">
+        <f>IF(E15="","",FF14+IF(C15="Pemasukan",E15,-E15))</f>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="str">
-        <v/>
-      </c>
-      <c r="B16" t="str">
-        <v/>
-      </c>
-      <c r="C16" t="str">
-        <v/>
-      </c>
-      <c r="D16" t="str">
-        <v/>
-      </c>
-      <c r="E16" t="str">
-        <v/>
-      </c>
-      <c r="F16" t="str">
-        <v/>
-      </c>
-      <c r="G16" t="str">
-        <v/>
-      </c>
-      <c r="H16" t="str">
-        <v/>
+      <c r="F16">
+        <f>IF(E16="","",FF15+IF(C16="Pemasukan",E16,-E16))</f>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="str">
-        <v/>
-      </c>
-      <c r="B17" t="str">
-        <v/>
-      </c>
-      <c r="C17" t="str">
-        <v/>
-      </c>
-      <c r="D17" t="str">
-        <v/>
-      </c>
-      <c r="E17" t="str">
-        <v/>
-      </c>
-      <c r="F17" t="str">
-        <v/>
-      </c>
-      <c r="G17" t="str">
-        <v/>
-      </c>
-      <c r="H17" t="str">
-        <v/>
+      <c r="F17">
+        <f>IF(E17="","",FF16+IF(C17="Pemasukan",E17,-E17))</f>
       </c>
     </row>
   </sheetData>
@@ -864,11 +654,11 @@
   <dimension ref="A1:F12"/>
   <cols>
     <col min="1" max="1" width="15.83203125" customWidth="1"/>
-    <col min="2" max="2" width="18.83203125" customWidth="1"/>
-    <col min="3" max="3" width="18.83203125" customWidth="1"/>
-    <col min="4" max="4" width="15.83203125" customWidth="1"/>
-    <col min="5" max="5" width="15.83203125" customWidth="1"/>
-    <col min="6" max="6" width="35.83203125" customWidth="1"/>
+    <col min="2" max="2" width="20.83203125" customWidth="1"/>
+    <col min="3" max="3" width="20.83203125" customWidth="1"/>
+    <col min="4" max="4" width="16.83203125" customWidth="1"/>
+    <col min="5" max="5" width="16.83203125" customWidth="1"/>
+    <col min="6" max="6" width="38.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -895,220 +685,130 @@
       <c r="A2" t="str">
         <v>Juni 2025</v>
       </c>
-      <c r="B2" t="str">
-        <v>Rp 1.000.000</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Rp 1.045.000</v>
-      </c>
-      <c r="D2" t="str">
-        <v>Rp 300.000</v>
-      </c>
-      <c r="E2" t="str">
-        <v>Rp 255.000</v>
+      <c r="B2">
+        <f>SUMIF('Buku Kas Harian'!C2:C500,"Pemasukan",'Buku Kas Harian'!E2:E500)</f>
+      </c>
+      <c r="C2">
+        <f>SUMIF('Buku Kas Harian'!C2:C500,"Pengeluaran",'Buku Kas Harian'!E2:E500)</f>
+      </c>
+      <c r="D2">
+        <v>300000</v>
+      </c>
+      <c r="E2">
+        <f>D2+B2-C2</f>
       </c>
       <c r="F2" t="str">
-        <v>Beli karpet baru (pengeluaran besar). Defisit wajar.</v>
+        <v>Beli karpet baru (pengeluaran besar). Wajar defisit.</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="str">
-        <v/>
-      </c>
-      <c r="B3" t="str">
-        <v/>
-      </c>
-      <c r="C3" t="str">
-        <v/>
-      </c>
-      <c r="D3" t="str">
-        <v/>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v/>
+      <c r="B3">
+        <f>SUMIF('Buku Kas Harian'!C2:C500,"Pemasukan",'Buku Kas Harian'!E2:E500)</f>
+      </c>
+      <c r="C3">
+        <f>SUMIF('Buku Kas Harian'!C2:C500,"Pengeluaran",'Buku Kas Harian'!E2:E500)</f>
+      </c>
+      <c r="E3">
+        <f>D3+B3-C3</f>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="str">
-        <v/>
-      </c>
-      <c r="B4" t="str">
-        <v/>
-      </c>
-      <c r="C4" t="str">
-        <v/>
-      </c>
-      <c r="D4" t="str">
-        <v/>
-      </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-      <c r="F4" t="str">
-        <v/>
+      <c r="B4">
+        <f>SUMIF('Buku Kas Harian'!C2:C500,"Pemasukan",'Buku Kas Harian'!E2:E500)</f>
+      </c>
+      <c r="C4">
+        <f>SUMIF('Buku Kas Harian'!C2:C500,"Pengeluaran",'Buku Kas Harian'!E2:E500)</f>
+      </c>
+      <c r="E4">
+        <f>D4+B4-C4</f>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="str">
-        <v/>
-      </c>
-      <c r="B5" t="str">
-        <v/>
-      </c>
-      <c r="C5" t="str">
-        <v/>
-      </c>
-      <c r="D5" t="str">
-        <v/>
-      </c>
-      <c r="E5" t="str">
-        <v/>
-      </c>
-      <c r="F5" t="str">
-        <v/>
+      <c r="B5">
+        <f>SUMIF('Buku Kas Harian'!C2:C500,"Pemasukan",'Buku Kas Harian'!E2:E500)</f>
+      </c>
+      <c r="C5">
+        <f>SUMIF('Buku Kas Harian'!C2:C500,"Pengeluaran",'Buku Kas Harian'!E2:E500)</f>
+      </c>
+      <c r="E5">
+        <f>D5+B5-C5</f>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="str">
-        <v/>
-      </c>
-      <c r="B6" t="str">
-        <v/>
-      </c>
-      <c r="C6" t="str">
-        <v/>
-      </c>
-      <c r="D6" t="str">
-        <v/>
-      </c>
-      <c r="E6" t="str">
-        <v/>
-      </c>
-      <c r="F6" t="str">
-        <v/>
+      <c r="B6">
+        <f>SUMIF('Buku Kas Harian'!C2:C500,"Pemasukan",'Buku Kas Harian'!E2:E500)</f>
+      </c>
+      <c r="C6">
+        <f>SUMIF('Buku Kas Harian'!C2:C500,"Pengeluaran",'Buku Kas Harian'!E2:E500)</f>
+      </c>
+      <c r="E6">
+        <f>D6+B6-C6</f>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="str">
-        <v/>
-      </c>
-      <c r="B7" t="str">
-        <v/>
-      </c>
-      <c r="C7" t="str">
-        <v/>
-      </c>
-      <c r="D7" t="str">
-        <v/>
-      </c>
-      <c r="E7" t="str">
-        <v/>
-      </c>
-      <c r="F7" t="str">
-        <v/>
+      <c r="B7">
+        <f>SUMIF('Buku Kas Harian'!C2:C500,"Pemasukan",'Buku Kas Harian'!E2:E500)</f>
+      </c>
+      <c r="C7">
+        <f>SUMIF('Buku Kas Harian'!C2:C500,"Pengeluaran",'Buku Kas Harian'!E2:E500)</f>
+      </c>
+      <c r="E7">
+        <f>D7+B7-C7</f>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="str">
-        <v/>
-      </c>
-      <c r="B8" t="str">
-        <v/>
-      </c>
-      <c r="C8" t="str">
-        <v/>
-      </c>
-      <c r="D8" t="str">
-        <v/>
-      </c>
-      <c r="E8" t="str">
-        <v/>
-      </c>
-      <c r="F8" t="str">
-        <v/>
+      <c r="B8">
+        <f>SUMIF('Buku Kas Harian'!C2:C500,"Pemasukan",'Buku Kas Harian'!E2:E500)</f>
+      </c>
+      <c r="C8">
+        <f>SUMIF('Buku Kas Harian'!C2:C500,"Pengeluaran",'Buku Kas Harian'!E2:E500)</f>
+      </c>
+      <c r="E8">
+        <f>D8+B8-C8</f>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="str">
-        <v/>
-      </c>
-      <c r="B9" t="str">
-        <v/>
-      </c>
-      <c r="C9" t="str">
-        <v/>
-      </c>
-      <c r="D9" t="str">
-        <v/>
-      </c>
-      <c r="E9" t="str">
-        <v/>
-      </c>
-      <c r="F9" t="str">
-        <v/>
+      <c r="B9">
+        <f>SUMIF('Buku Kas Harian'!C2:C500,"Pemasukan",'Buku Kas Harian'!E2:E500)</f>
+      </c>
+      <c r="C9">
+        <f>SUMIF('Buku Kas Harian'!C2:C500,"Pengeluaran",'Buku Kas Harian'!E2:E500)</f>
+      </c>
+      <c r="E9">
+        <f>D9+B9-C9</f>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="str">
-        <v/>
-      </c>
-      <c r="B10" t="str">
-        <v/>
-      </c>
-      <c r="C10" t="str">
-        <v/>
-      </c>
-      <c r="D10" t="str">
-        <v/>
-      </c>
-      <c r="E10" t="str">
-        <v/>
-      </c>
-      <c r="F10" t="str">
-        <v/>
+      <c r="B10">
+        <f>SUMIF('Buku Kas Harian'!C2:C500,"Pemasukan",'Buku Kas Harian'!E2:E500)</f>
+      </c>
+      <c r="C10">
+        <f>SUMIF('Buku Kas Harian'!C2:C500,"Pengeluaran",'Buku Kas Harian'!E2:E500)</f>
+      </c>
+      <c r="E10">
+        <f>D10+B10-C10</f>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="str">
-        <v/>
-      </c>
-      <c r="B11" t="str">
-        <v/>
-      </c>
-      <c r="C11" t="str">
-        <v/>
-      </c>
-      <c r="D11" t="str">
-        <v/>
-      </c>
-      <c r="E11" t="str">
-        <v/>
-      </c>
-      <c r="F11" t="str">
-        <v/>
+      <c r="B11">
+        <f>SUMIF('Buku Kas Harian'!C2:C500,"Pemasukan",'Buku Kas Harian'!E2:E500)</f>
+      </c>
+      <c r="C11">
+        <f>SUMIF('Buku Kas Harian'!C2:C500,"Pengeluaran",'Buku Kas Harian'!E2:E500)</f>
+      </c>
+      <c r="E11">
+        <f>D11+B11-C11</f>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="str">
-        <v/>
-      </c>
-      <c r="B12" t="str">
-        <v/>
-      </c>
-      <c r="C12" t="str">
-        <v/>
-      </c>
-      <c r="D12" t="str">
-        <v/>
-      </c>
-      <c r="E12" t="str">
-        <v/>
-      </c>
-      <c r="F12" t="str">
-        <v/>
+      <c r="B12">
+        <f>SUMIF('Buku Kas Harian'!C2:C500,"Pemasukan",'Buku Kas Harian'!E2:E500)</f>
+      </c>
+      <c r="C12">
+        <f>SUMIF('Buku Kas Harian'!C2:C500,"Pengeluaran",'Buku Kas Harian'!E2:E500)</f>
+      </c>
+      <c r="E12">
+        <f>D12+B12-C12</f>
       </c>
     </row>
   </sheetData>
